--- a/进取组类型.xlsx
+++ b/进取组类型.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN筛选器v1\screener\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN_老板候选池v8_转换\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BF1CF7-38A0-435C-90B7-F78628574409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B164D2-FEE6-40EC-AF39-659FCCA57373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="66">
   <si>
     <t>区域</t>
   </si>
@@ -52,163 +52,172 @@
     <t>美股</t>
   </si>
   <si>
-    <t>APLD US</t>
-  </si>
-  <si>
-    <t>Applied Digital</t>
-  </si>
-  <si>
-    <t>信息技术服务</t>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AI 芯片</t>
   </si>
   <si>
     <t>欧式敲入</t>
   </si>
   <si>
-    <t>HPE US</t>
-  </si>
-  <si>
-    <t>慧与科技</t>
-  </si>
-  <si>
-    <t>通讯设备</t>
-  </si>
-  <si>
-    <t>MU US</t>
-  </si>
-  <si>
-    <t>美光科技</t>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔</t>
+  </si>
+  <si>
+    <t>AI 服务器</t>
+  </si>
+  <si>
+    <t>LRCX US</t>
+  </si>
+  <si>
+    <t>泛林集团</t>
+  </si>
+  <si>
+    <t>半导体设备</t>
+  </si>
+  <si>
+    <t>DDOG US</t>
+  </si>
+  <si>
+    <t>Datadog</t>
+  </si>
+  <si>
+    <t>可观测性</t>
+  </si>
+  <si>
+    <t>CIEN US</t>
+  </si>
+  <si>
+    <t>Ciena</t>
+  </si>
+  <si>
+    <t>光网络</t>
+  </si>
+  <si>
+    <t>AMAT US</t>
+  </si>
+  <si>
+    <t>应用材料</t>
+  </si>
+  <si>
+    <t>TSM US</t>
+  </si>
+  <si>
+    <t>台积电</t>
+  </si>
+  <si>
+    <t>晶圆代工</t>
+  </si>
+  <si>
+    <t>MCHP US</t>
+  </si>
+  <si>
+    <t>微芯</t>
   </si>
   <si>
     <t>半导体</t>
   </si>
   <si>
-    <t>APP US</t>
-  </si>
-  <si>
-    <t>Applovin</t>
-  </si>
-  <si>
-    <t>广告代理</t>
-  </si>
-  <si>
-    <t>LITE US</t>
-  </si>
-  <si>
-    <t>Lumentum</t>
-  </si>
-  <si>
-    <t>SNOW US</t>
-  </si>
-  <si>
-    <t>Snowflake</t>
-  </si>
-  <si>
-    <t>应用软件</t>
-  </si>
-  <si>
-    <t>CIEN US</t>
-  </si>
-  <si>
-    <t>Ciena</t>
-  </si>
-  <si>
-    <t>QBTS US</t>
-  </si>
-  <si>
-    <t>D-Wave Quantum</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>ORCL US</t>
-  </si>
-  <si>
-    <t>甲骨文</t>
-  </si>
-  <si>
-    <t>软件基础设施</t>
-  </si>
-  <si>
-    <t>SMTC US</t>
-  </si>
-  <si>
-    <t>先科电子</t>
-  </si>
-  <si>
-    <t>NOK US</t>
-  </si>
-  <si>
-    <t>诺基亚</t>
-  </si>
-  <si>
-    <t>CRWV US</t>
-  </si>
-  <si>
-    <t>CoreWeave</t>
-  </si>
-  <si>
-    <t>AVGO US</t>
-  </si>
-  <si>
-    <t>博通</t>
+    <t>ADI US</t>
+  </si>
+  <si>
+    <t>亚德诺</t>
+  </si>
+  <si>
+    <t>KLAC US</t>
+  </si>
+  <si>
+    <t>科磊</t>
+  </si>
+  <si>
+    <t>DKNG US</t>
+  </si>
+  <si>
+    <t>DraftKings</t>
+  </si>
+  <si>
+    <t>体育博彩</t>
+  </si>
+  <si>
+    <t>LLY US</t>
+  </si>
+  <si>
+    <t>礼来</t>
+  </si>
+  <si>
+    <t>制药</t>
+  </si>
+  <si>
+    <t>COIN US</t>
+  </si>
+  <si>
+    <t>Coinbase</t>
+  </si>
+  <si>
+    <t>加密</t>
+  </si>
+  <si>
+    <t>HOOD US</t>
+  </si>
+  <si>
+    <t>Robinhood</t>
+  </si>
+  <si>
+    <t>券商</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>6651 HK</t>
-  </si>
-  <si>
-    <t>五一视界</t>
-  </si>
-  <si>
-    <t>数码解决方案服务</t>
-  </si>
-  <si>
-    <t>6082 HK</t>
-  </si>
-  <si>
-    <t>壁仞科技</t>
-  </si>
-  <si>
-    <t>9992 HK</t>
-  </si>
-  <si>
-    <t>泡泡玛特</t>
-  </si>
-  <si>
-    <t>玩具及消闲用品</t>
-  </si>
-  <si>
-    <t>2259 HK</t>
-  </si>
-  <si>
-    <t>紫金黄金国际</t>
-  </si>
-  <si>
-    <t>黄金及贵金属</t>
-  </si>
-  <si>
-    <t>3986 HK</t>
-  </si>
-  <si>
-    <t>兆易创新</t>
-  </si>
-  <si>
-    <t>6809 HK</t>
-  </si>
-  <si>
-    <t>澜起科技</t>
-  </si>
-  <si>
-    <t>3323 HK</t>
-  </si>
-  <si>
-    <t>中国建材</t>
-  </si>
-  <si>
-    <t>建筑材料</t>
+    <t>1347 HK</t>
+  </si>
+  <si>
+    <t>华虹半导体</t>
+  </si>
+  <si>
+    <t>981 HK</t>
+  </si>
+  <si>
+    <t>中芯国际</t>
+  </si>
+  <si>
+    <t>522 HK</t>
+  </si>
+  <si>
+    <t>ASMPT</t>
+  </si>
+  <si>
+    <t>2018 HK</t>
+  </si>
+  <si>
+    <t>瑞声科技</t>
+  </si>
+  <si>
+    <t>声学/光学</t>
+  </si>
+  <si>
+    <t>992 HK</t>
+  </si>
+  <si>
+    <t>联想</t>
+  </si>
+  <si>
+    <t>AI/PC</t>
+  </si>
+  <si>
+    <t>2359 HK</t>
+  </si>
+  <si>
+    <t>药明康德</t>
+  </si>
+  <si>
+    <t>CDMO</t>
   </si>
 </sst>
 </file>
@@ -581,7 +590,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -643,7 +652,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" s="3">
-        <v>0.44219999999999998</v>
+        <v>0.31419999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -672,7 +681,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" s="3">
-        <v>0.28460000000000002</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -701,7 +710,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" s="3">
-        <v>0.47189999999999999</v>
+        <v>0.34670000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -730,7 +739,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" s="3">
-        <v>0.30719999999999997</v>
+        <v>0.26540000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -744,7 +753,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2">
         <v>0.8</v>
@@ -759,7 +768,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" s="3">
-        <v>0.47539999999999999</v>
+        <v>0.41970000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -767,13 +776,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2">
         <v>0.8</v>
@@ -788,7 +797,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" s="3">
-        <v>0.25419999999999998</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -802,7 +811,7 @@
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2">
         <v>0.8</v>
@@ -817,7 +826,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" s="3">
-        <v>0.41810000000000003</v>
+        <v>0.1676</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -825,13 +834,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2">
         <v>0.8</v>
@@ -846,7 +855,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" s="3">
-        <v>0.4793</v>
+        <v>0.22650000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -854,14 +863,14 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" s="2">
         <v>0.8</v>
       </c>
@@ -875,7 +884,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" s="3">
-        <v>0.21249999999999999</v>
+        <v>0.16850000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -904,7 +913,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" s="3">
-        <v>0.46779999999999999</v>
+        <v>0.34970000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -918,7 +927,7 @@
         <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2">
         <v>0.8</v>
@@ -933,7 +942,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" s="3">
-        <v>0.31819999999999998</v>
+        <v>0.20100000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -941,13 +950,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2">
         <v>0.8</v>
@@ -962,7 +971,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" s="3">
-        <v>0.43659999999999999</v>
+        <v>8.4099999999999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -970,13 +979,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2">
         <v>0.8</v>
@@ -991,21 +1000,21 @@
         <v>1.01</v>
       </c>
       <c r="I14" s="3">
-        <v>0.16250000000000001</v>
+        <v>0.33960000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2">
         <v>0.8</v>
@@ -1020,21 +1029,21 @@
         <v>1.01</v>
       </c>
       <c r="I15" s="3">
-        <v>0.34570000000000001</v>
+        <v>0.29499999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2">
         <v>0.8</v>
@@ -1049,21 +1058,21 @@
         <v>1.01</v>
       </c>
       <c r="I16" s="3">
-        <v>0.33729999999999999</v>
+        <v>0.37140000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2">
         <v>0.8</v>
@@ -1078,21 +1087,21 @@
         <v>1.01</v>
       </c>
       <c r="I17" s="3">
-        <v>0.156</v>
+        <v>0.24199999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2">
         <v>0.8</v>
@@ -1107,21 +1116,21 @@
         <v>1.01</v>
       </c>
       <c r="I18" s="3">
-        <v>0.22689999999999999</v>
+        <v>0.23200000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2">
         <v>0.8</v>
@@ -1136,21 +1145,21 @@
         <v>1.01</v>
       </c>
       <c r="I19" s="3">
-        <v>0.4425</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2">
         <v>0.8</v>
@@ -1165,21 +1174,21 @@
         <v>1.01</v>
       </c>
       <c r="I20" s="3">
-        <v>0.37609999999999999</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2">
         <v>0.8</v>
@@ -1194,7 +1203,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" s="3">
-        <v>0.2379</v>
+        <v>0.1227</v>
       </c>
     </row>
   </sheetData>
